--- a/Data/National Accounts/PSA-19EDUC_2018PSNA_Ann.xlsx
+++ b/Data/National Accounts/PSA-19EDUC_2018PSNA_Ann.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of January 2026\Tables\Prelim Q4 2025\NAP Q1 2000 to Q4 2025\Annl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Annl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91E9C45F-96F4-4EA2-A686-723A8D1D709C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D539DB6-151F-40E8-868C-68000DF3275F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EDUC" sheetId="2" r:id="rId1"/>
@@ -610,9 +610,6 @@
     <t>2023 - 2024</t>
   </si>
   <si>
-    <t>As of January 2026</t>
-  </si>
-  <si>
     <t>Annual 2000 to 2025</t>
   </si>
   <si>
@@ -620,6 +617,9 @@
   </si>
   <si>
     <t>2024 - 2025</t>
+  </si>
+  <si>
+    <t>As of April 2026</t>
   </si>
 </sst>
 </file>
@@ -23618,7 +23618,7 @@
     </row>
     <row r="3" spans="1:96" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:96" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -23631,7 +23631,7 @@
     </row>
     <row r="6" spans="1:96" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:96" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -23888,10 +23888,10 @@
         <v>673342.09069326171</v>
       </c>
       <c r="Z12" s="9">
-        <v>716699.53101314208</v>
+        <v>718193.97405520896</v>
       </c>
       <c r="AA12" s="9">
-        <v>813281.85014137789</v>
+        <v>807493.97412136453</v>
       </c>
       <c r="AB12" s="10"/>
       <c r="AC12" s="10"/>
@@ -24040,10 +24040,10 @@
         <v>296208.0478517508</v>
       </c>
       <c r="Z13" s="9">
-        <v>336380.8867773618</v>
+        <v>337369.98738575558</v>
       </c>
       <c r="AA13" s="9">
-        <v>373989.47632272821</v>
+        <v>375428.14811863506</v>
       </c>
       <c r="AB13" s="10"/>
       <c r="AC13" s="10"/>
@@ -24290,10 +24290,10 @@
         <v>969550.13854501257</v>
       </c>
       <c r="Z15" s="15">
-        <v>1053080.4177905039</v>
+        <v>1055563.9614409646</v>
       </c>
       <c r="AA15" s="15">
-        <v>1187271.3264641061</v>
+        <v>1182922.1222399995</v>
       </c>
       <c r="AB15" s="10"/>
       <c r="AC15" s="10"/>
@@ -24685,7 +24685,7 @@
     </row>
     <row r="22" spans="1:96" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -24776,7 +24776,7 @@
     </row>
     <row r="25" spans="1:96" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -25085,10 +25085,10 @@
         <v>573898.55689843139</v>
       </c>
       <c r="Z31" s="9">
-        <v>588967.98929395166</v>
+        <v>591829.74004738824</v>
       </c>
       <c r="AA31" s="9">
-        <v>643703.10486624856</v>
+        <v>641294.48093538068</v>
       </c>
       <c r="AB31" s="10"/>
       <c r="AC31" s="10"/>
@@ -25237,10 +25237,10 @@
         <v>270819.13825145434</v>
       </c>
       <c r="Z32" s="9">
-        <v>293083.03358792962</v>
+        <v>293894.27661017497</v>
       </c>
       <c r="AA32" s="9">
-        <v>312036.72848186275</v>
+        <v>313166.47571104113</v>
       </c>
       <c r="AB32" s="10"/>
       <c r="AC32" s="10"/>
@@ -25487,10 +25487,10 @@
         <v>844717.69514988572</v>
       </c>
       <c r="Z34" s="15">
-        <v>882051.02288188133</v>
+        <v>885724.01665756316</v>
       </c>
       <c r="AA34" s="15">
-        <v>955739.83334811125</v>
+        <v>954460.95664642181</v>
       </c>
       <c r="AB34" s="10"/>
       <c r="AC34" s="10"/>
@@ -25882,7 +25882,7 @@
     </row>
     <row r="41" spans="1:96" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -25973,7 +25973,7 @@
     </row>
     <row r="44" spans="1:96" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -26170,7 +26170,7 @@
         <v>46</v>
       </c>
       <c r="Z48" s="20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA48" s="20"/>
     </row>
@@ -26277,10 +26277,10 @@
         <v>8.6961709202647768</v>
       </c>
       <c r="Y50" s="21">
-        <v>6.4391400625557651</v>
+        <v>6.6610841624007833</v>
       </c>
       <c r="Z50" s="21">
-        <v>13.475984697758193</v>
+        <v>12.433966768327537</v>
       </c>
       <c r="AA50" s="21"/>
       <c r="AB50" s="10"/>
@@ -26422,10 +26422,10 @@
         <v>13.525320688487923</v>
       </c>
       <c r="Y51" s="21">
-        <v>13.562372534090343</v>
+        <v>13.89629344392624</v>
       </c>
       <c r="Z51" s="21">
-        <v>11.180358642153806</v>
+        <v>11.28083770218808</v>
       </c>
       <c r="AA51" s="21"/>
       <c r="AB51" s="10"/>
@@ -26660,10 +26660,10 @@
         <v>10.127369124640538</v>
       </c>
       <c r="Y53" s="21">
-        <v>8.6153645824695388</v>
+        <v>8.8715188082002072</v>
       </c>
       <c r="Z53" s="21">
-        <v>12.742702874976231</v>
+        <v>12.065413887868687</v>
       </c>
       <c r="AA53" s="21"/>
       <c r="AB53" s="10"/>
@@ -27041,7 +27041,7 @@
     </row>
     <row r="60" spans="1:91" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -27132,7 +27132,7 @@
     </row>
     <row r="63" spans="1:91" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -27329,7 +27329,7 @@
         <v>46</v>
       </c>
       <c r="Z67" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA67" s="7"/>
     </row>
@@ -27436,10 +27436,10 @@
         <v>4.5213080862338302</v>
       </c>
       <c r="Y69" s="21">
-        <v>2.6258007124048532</v>
+        <v>3.1244516880934299</v>
       </c>
       <c r="Z69" s="21">
-        <v>9.2933939649101802</v>
+        <v>8.35793430793656</v>
       </c>
       <c r="AA69" s="21"/>
       <c r="AB69" s="10"/>
@@ -27581,10 +27581,10 @@
         <v>9.6077080512194613</v>
       </c>
       <c r="Y70" s="21">
-        <v>8.2209460824010705</v>
+        <v>8.5204976678182334</v>
       </c>
       <c r="Z70" s="21">
-        <v>6.4670051561503072</v>
+        <v>6.557527871299456</v>
       </c>
       <c r="AA70" s="21"/>
       <c r="AB70" s="10"/>
@@ -27819,10 +27819,10 @@
         <v>6.0998345886813325</v>
       </c>
       <c r="Y72" s="21">
-        <v>4.4196218389116666</v>
+        <v>4.8544409266105646</v>
       </c>
       <c r="Z72" s="21">
-        <v>8.3542571296465411</v>
+        <v>7.7605369952877368</v>
       </c>
       <c r="AA72" s="21"/>
       <c r="AB72" s="10"/>
@@ -28170,7 +28170,7 @@
     </row>
     <row r="78" spans="1:92" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -28261,7 +28261,7 @@
     </row>
     <row r="81" spans="1:92" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -28570,10 +28570,10 @@
         <v>117.3277197859255</v>
       </c>
       <c r="Z87" s="21">
-        <v>121.68734872540587</v>
+        <v>121.35145050292719</v>
       </c>
       <c r="AA87" s="21">
-        <v>126.34424845758126</v>
+        <v>125.91625191340619</v>
       </c>
       <c r="AB87" s="10"/>
       <c r="AC87" s="10"/>
@@ -28718,10 +28718,10 @@
         <v>109.37485798242331</v>
       </c>
       <c r="Z88" s="21">
-        <v>114.77323769287455</v>
+        <v>114.79297633048068</v>
       </c>
       <c r="AA88" s="21">
-        <v>119.85431270936635</v>
+        <v>119.88133380695665</v>
       </c>
       <c r="AB88" s="10"/>
       <c r="AC88" s="10"/>
@@ -28960,10 +28960,10 @@
         <v>114.77800738777904</v>
       </c>
       <c r="Z90" s="21">
-        <v>119.38996616656334</v>
+        <v>119.17526696682819</v>
       </c>
       <c r="AA90" s="21">
-        <v>124.22536814280332</v>
+        <v>123.93614573783039</v>
       </c>
       <c r="AB90" s="10"/>
       <c r="AC90" s="10"/>
@@ -29213,7 +29213,7 @@
     </row>
     <row r="97" spans="1:96" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -29304,7 +29304,7 @@
     </row>
     <row r="100" spans="1:96" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -29613,10 +29613,10 @@
         <v>69.448919032050753</v>
       </c>
       <c r="Z106" s="21">
-        <v>68.057435966463842</v>
+        <v>68.038887295355622</v>
       </c>
       <c r="AA106" s="21">
-        <v>68.500083511952411</v>
+        <v>68.262648820218317</v>
       </c>
       <c r="AB106" s="10"/>
       <c r="AC106" s="10"/>
@@ -29765,10 +29765,10 @@
         <v>30.55108096794924</v>
       </c>
       <c r="Z107" s="21">
-        <v>31.942564033536158</v>
+        <v>31.961112704644375</v>
       </c>
       <c r="AA107" s="21">
-        <v>31.499916488047585</v>
+        <v>31.737351179781687</v>
       </c>
       <c r="AB107" s="10"/>
       <c r="AC107" s="10"/>
@@ -30410,7 +30410,7 @@
     </row>
     <row r="116" spans="1:96" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -30501,7 +30501,7 @@
     </row>
     <row r="119" spans="1:96" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -30810,10 +30810,10 @@
         <v>67.939686855571253</v>
       </c>
       <c r="Z125" s="21">
-        <v>66.772553289450968</v>
+        <v>66.818752672052725</v>
       </c>
       <c r="AA125" s="21">
-        <v>67.351289797271761</v>
+        <v>67.189179030289765</v>
       </c>
       <c r="AB125" s="10"/>
       <c r="AC125" s="10"/>
@@ -30962,10 +30962,10 @@
         <v>32.06031314442874</v>
       </c>
       <c r="Z126" s="21">
-        <v>33.22744671054901</v>
+        <v>33.181247327947275</v>
       </c>
       <c r="AA126" s="21">
-        <v>32.648710202728246</v>
+        <v>32.810820969710242</v>
       </c>
       <c r="AB126" s="10"/>
       <c r="AC126" s="10"/>
